--- a/Employee_Reports_wi52/John Errol Para Marino Q0393.xlsx
+++ b/Employee_Reports_wi52/John Errol Para Marino Q0393.xlsx
@@ -569,11 +569,11 @@
         </is>
       </c>
       <c r="H3" s="3" t="n">
-        <v>-224</v>
+        <v>-232</v>
       </c>
       <c r="I3" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J3" s="3" t="inlineStr">
@@ -618,11 +618,11 @@
         </is>
       </c>
       <c r="H4" s="4" t="n">
-        <v>343</v>
+        <v>335</v>
       </c>
       <c r="I4" s="4" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J4" s="4" t="inlineStr">
@@ -667,11 +667,11 @@
         </is>
       </c>
       <c r="H5" s="4" t="n">
-        <v>342</v>
+        <v>334</v>
       </c>
       <c r="I5" s="4" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J5" s="4" t="inlineStr">
@@ -716,11 +716,11 @@
         </is>
       </c>
       <c r="H6" s="4" t="n">
-        <v>343</v>
+        <v>335</v>
       </c>
       <c r="I6" s="4" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J6" s="4" t="inlineStr">
@@ -753,11 +753,11 @@
         </is>
       </c>
       <c r="H7" s="4" t="n">
-        <v>342</v>
+        <v>334</v>
       </c>
       <c r="I7" s="4" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J7" s="4" t="inlineStr">
@@ -802,11 +802,11 @@
         </is>
       </c>
       <c r="H8" s="4" t="n">
-        <v>448</v>
+        <v>440</v>
       </c>
       <c r="I8" s="4" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J8" s="4" t="inlineStr">
@@ -851,11 +851,11 @@
         </is>
       </c>
       <c r="H9" s="4" t="n">
-        <v>448</v>
+        <v>440</v>
       </c>
       <c r="I9" s="4" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J9" s="4" t="inlineStr">
@@ -900,11 +900,11 @@
         </is>
       </c>
       <c r="H10" s="4" t="n">
-        <v>448</v>
+        <v>440</v>
       </c>
       <c r="I10" s="4" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J10" s="4" t="inlineStr">
@@ -949,11 +949,11 @@
         </is>
       </c>
       <c r="H11" s="4" t="n">
-        <v>449</v>
+        <v>441</v>
       </c>
       <c r="I11" s="4" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J11" s="4" t="inlineStr">
@@ -986,11 +986,11 @@
         </is>
       </c>
       <c r="H12" s="4" t="n">
-        <v>497</v>
+        <v>489</v>
       </c>
       <c r="I12" s="4" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J12" s="4" t="inlineStr">
